--- a/product_upload/packages/6/file.xlsx
+++ b/product_upload/packages/6/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR101"/>
+  <dimension ref="A1:AS101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -639,6 +639,11 @@
         </is>
       </c>
       <c r="AR1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -667,7 +672,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -816,6 +821,11 @@
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>MIMPARA 60MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>SKU-539C40F38D4F</t>
         </is>
       </c>
@@ -843,7 +853,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -996,6 +1006,11 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
+          <t>MIMPARA 90MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>SKU-43105051482F</t>
         </is>
       </c>
@@ -1023,7 +1038,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1180,6 +1195,11 @@
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr">
         <is>
+          <t>MINIMS TETRACAINE HCL 1%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>SKU-729BCD598478</t>
         </is>
       </c>
@@ -1207,7 +1227,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1360,6 +1380,11 @@
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr">
         <is>
+          <t>MINIMS SODIUM CHLORIDE 0.9%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
           <t>SKU-B1D3C0B3173C</t>
         </is>
       </c>
@@ -1387,7 +1412,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1536,6 +1561,11 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>MINIMS PILOCARPINE 2%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
           <t>SKU-50D6D64E8290</t>
         </is>
       </c>
@@ -1563,7 +1593,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1716,6 +1746,11 @@
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>MINIMS PHENYLEPHRINE HCL 10%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>SKU-CBAE0AA8D24B</t>
         </is>
       </c>
@@ -1743,7 +1778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1896,6 +1931,11 @@
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>MINIMS PHENYLEPHRINE 2.5% W-V</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
           <t>SKU-DF72348AFBC4</t>
         </is>
       </c>
@@ -1923,7 +1963,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2084,6 +2124,11 @@
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr">
         <is>
+          <t>MICONAZ 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
           <t>SKU-E99C04DC749C</t>
         </is>
       </c>
@@ -2111,7 +2156,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2272,6 +2317,11 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
+          <t>MINIMS OXYBUPROCAINE HCL 0.4%</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
           <t>SKU-AF74FFB3FC92</t>
         </is>
       </c>
@@ -2299,7 +2349,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2448,6 +2498,11 @@
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>MINIMS FLUORESCEIN SODIUM 2%</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
           <t>SKU-C9773064B349</t>
         </is>
       </c>
@@ -2475,7 +2530,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2636,6 +2691,11 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>MINIMS CYCLOPENTOLATE HCL 1%</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
           <t>SKU-FD5B990015B1</t>
         </is>
       </c>
@@ -2663,7 +2723,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2812,6 +2872,11 @@
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr">
         <is>
+          <t>MINIMS CYCLOPENTOLATE HCL 0.5%</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
           <t>SKU-1608B3E97F32</t>
         </is>
       </c>
@@ -2839,7 +2904,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3000,6 +3065,11 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>MINIMS CHLORAMPHENICOL 0.5%</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
           <t>SKU-7693B490DD20</t>
         </is>
       </c>
@@ -3027,7 +3097,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3184,6 +3254,11 @@
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>MINIMS ATROPINE SULPHATE 1%</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
           <t>SKU-48E02E3EA89A</t>
         </is>
       </c>
@@ -3211,7 +3286,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3360,6 +3435,11 @@
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>MINIMS LIDOCAINE and FLUORESCEIN</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
           <t>SKU-3E2F5C5B392A</t>
         </is>
       </c>
@@ -3387,7 +3467,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3544,6 +3624,11 @@
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>MICOCORT CREAM</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
           <t>SKU-320265955D2E</t>
         </is>
       </c>
@@ -3571,7 +3656,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3726,6 +3811,11 @@
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr">
         <is>
+          <t>MICARDIS PLUS</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
           <t>SKU-71C9AC51216D</t>
         </is>
       </c>
@@ -3753,7 +3843,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3914,6 +4004,11 @@
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="inlineStr">
         <is>
+          <t>METFORMIN HEXAL 1000 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
           <t>SKU-D643D94F0A7E</t>
         </is>
       </c>
@@ -3941,7 +4036,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4094,6 +4189,11 @@
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr">
         <is>
+          <t>METFOR 850 MG TAB</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
           <t>SKU-D646C23BCF1D</t>
         </is>
       </c>
@@ -4121,7 +4221,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4282,6 +4382,11 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
+          <t>METFOR 500</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
           <t>SKU-C517852F3B58</t>
         </is>
       </c>
@@ -4309,7 +4414,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4478,6 +4583,11 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>METHOTREXATE 2.5MG TAB.</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
           <t>SKU-9DBF4C9DC41D</t>
         </is>
       </c>
@@ -4505,7 +4615,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4668,6 +4778,11 @@
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>MICARDIS 80 MG TAB</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
           <t>SKU-44DE602E00F1</t>
         </is>
       </c>
@@ -4695,7 +4810,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4858,6 +4973,11 @@
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr">
         <is>
+          <t>MICARDIS 40 MG TAB</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
           <t>SKU-089BF1FEB17D</t>
         </is>
       </c>
@@ -4885,7 +5005,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5042,6 +5162,11 @@
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr">
         <is>
+          <t>MEVA 135MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
           <t>SKU-49A9FE0807A8</t>
         </is>
       </c>
@@ -5069,7 +5194,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5236,6 +5361,11 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
+          <t xml:space="preserve">MICARDIS PLUS </t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
           <t>SKU-895101D525AC</t>
         </is>
       </c>
@@ -5263,7 +5393,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5412,6 +5542,11 @@
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="inlineStr">
         <is>
+          <t>METOSIL TAB 10MG</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
           <t>SKU-BB1B499ECEA2</t>
         </is>
       </c>
@@ -5439,7 +5574,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5596,6 +5731,11 @@
       <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="inlineStr">
         <is>
+          <t>METHYCOBAL 500 MCG TABLET</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
           <t>SKU-66060F1EE290</t>
         </is>
       </c>
@@ -5623,7 +5763,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5768,6 +5908,11 @@
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr">
         <is>
+          <t>MINIRIN MELT 240MCG ORAL LYOPHILISATE TABLET</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
           <t>SKU-C1479DB9A4A0</t>
         </is>
       </c>
@@ -5795,7 +5940,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5952,6 +6097,11 @@
       <c r="AQ30" t="inlineStr"/>
       <c r="AR30" t="inlineStr">
         <is>
+          <t>MINIRIN MELT 120 MCG LYOPHILIZED TABLET</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
           <t>SKU-72AEC9A28CFF</t>
         </is>
       </c>
@@ -5979,7 +6129,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6124,6 +6274,11 @@
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr">
         <is>
+          <t>MUCOFALK</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
           <t>SKU-053BC909DBCA</t>
         </is>
       </c>
@@ -6151,7 +6306,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6304,6 +6459,11 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
+          <t>MUCOFALK</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
           <t>SKU-B4F4147043BA</t>
         </is>
       </c>
@@ -6331,7 +6491,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6484,6 +6644,11 @@
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr">
         <is>
+          <t>MUCINEX 600MG EXTENDED RELEASE BI-LAYER TABLET</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
           <t>SKU-5F8696D8813B</t>
         </is>
       </c>
@@ -6511,7 +6676,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6656,6 +6821,11 @@
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="inlineStr">
         <is>
+          <t>MOVEN 7.5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
           <t>SKU-D33560BB9239</t>
         </is>
       </c>
@@ -6683,7 +6853,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6836,6 +7006,11 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
+          <t>MOVEN 7.5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
           <t>SKU-30667FCAFD41</t>
         </is>
       </c>
@@ -6863,7 +7038,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7008,6 +7183,11 @@
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr">
         <is>
+          <t>MOVEN 15MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
           <t>SKU-E17CA828C0F3</t>
         </is>
       </c>
@@ -7035,7 +7215,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7184,6 +7364,11 @@
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr">
         <is>
+          <t>MOVEN 15MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
           <t>SKU-E068355AF75E</t>
         </is>
       </c>
@@ -7211,7 +7396,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7372,6 +7557,11 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
+          <t>MOTILIUM TAB 10MG</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
           <t>SKU-BD7E01B84149</t>
         </is>
       </c>
@@ -7399,7 +7589,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7560,6 +7750,11 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
+          <t>MOTILIUM SYRUP 0.1%</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
           <t>SKU-36F4B8204F78</t>
         </is>
       </c>
@@ -7587,7 +7782,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7744,6 +7939,11 @@
       <c r="AQ40" t="inlineStr"/>
       <c r="AR40" t="inlineStr">
         <is>
+          <t>MONUROL 3G SACHETS</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
           <t>SKU-409459049E76</t>
         </is>
       </c>
@@ -7771,7 +7971,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7934,6 +8134,11 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
+          <t>MONTEL 5MG CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
           <t>SKU-C7C449AC8298</t>
         </is>
       </c>
@@ -7961,7 +8166,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8118,6 +8323,11 @@
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="inlineStr">
         <is>
+          <t>MONTEL 4MG GRANULES</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
           <t>SKU-BC91A742C847</t>
         </is>
       </c>
@@ -8145,7 +8355,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8308,6 +8518,11 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
+          <t>MONTEL 4MG CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
           <t>SKU-DCCB73C20ED6</t>
         </is>
       </c>
@@ -8335,7 +8550,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8488,6 +8703,11 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
+          <t>MUCOFREE 4MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
           <t>SKU-4987739DA4B8</t>
         </is>
       </c>
@@ -8515,7 +8735,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8672,6 +8892,11 @@
       <c r="AQ45" t="inlineStr"/>
       <c r="AR45" t="inlineStr">
         <is>
+          <t>MUCOGEL</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
           <t>SKU-A2A2ACA718DF</t>
         </is>
       </c>
@@ -8699,7 +8924,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8856,6 +9081,11 @@
       <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="inlineStr">
         <is>
+          <t>MUCOSOLVAN 30MG-5ML ORAL LIQUID</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
           <t>SKU-81A2357EA845</t>
         </is>
       </c>
@@ -8883,7 +9113,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9040,6 +9270,11 @@
       <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="inlineStr">
         <is>
+          <t>MYCOSAT 100,000IU\ML ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
           <t>SKU-109FBBD89D8C</t>
         </is>
       </c>
@@ -9067,7 +9302,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9224,6 +9459,11 @@
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="inlineStr">
         <is>
+          <t>MYCOLESS CREAM</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
           <t>SKU-122B70F3BB92</t>
         </is>
       </c>
@@ -9251,7 +9491,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9408,6 +9648,11 @@
       <c r="AQ49" t="inlineStr"/>
       <c r="AR49" t="inlineStr">
         <is>
+          <t>MONTEL 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
           <t>SKU-1BB77EF3DCD8</t>
         </is>
       </c>
@@ -9435,7 +9680,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9588,6 +9833,11 @@
       <c r="AQ50" t="inlineStr"/>
       <c r="AR50" t="inlineStr">
         <is>
+          <t>MYCOHEAL 400MG VAGINAL SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
           <t>SKU-C9B3809EC45A</t>
         </is>
       </c>
@@ -9615,7 +9865,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9772,6 +10022,11 @@
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="inlineStr">
         <is>
+          <t>MYCOHEAL 2% ORAL GEL</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
           <t>SKU-D5EC6071352B</t>
         </is>
       </c>
@@ -9799,7 +10054,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9944,6 +10199,11 @@
       <c r="AQ52" t="inlineStr"/>
       <c r="AR52" t="inlineStr">
         <is>
+          <t>MULTIVITOL FORTE SYRUP</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
           <t>SKU-3F785EFD23CA</t>
         </is>
       </c>
@@ -9971,7 +10231,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10128,6 +10388,11 @@
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="inlineStr">
         <is>
+          <t>MONOZIDE 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
           <t>SKU-A826C539E19F</t>
         </is>
       </c>
@@ -10155,7 +10420,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10312,6 +10577,11 @@
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="inlineStr">
         <is>
+          <t>MONOZIDE 12.5MG TAB</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
           <t>SKU-73514DA3E2A4</t>
         </is>
       </c>
@@ -10339,7 +10609,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10500,6 +10770,11 @@
       </c>
       <c r="AR55" t="inlineStr">
         <is>
+          <t>MIRZAGEN 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
           <t>SKU-C664F4ED59C5</t>
         </is>
       </c>
@@ -10527,7 +10802,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10684,6 +10959,11 @@
       <c r="AQ56" t="inlineStr"/>
       <c r="AR56" t="inlineStr">
         <is>
+          <t>MIRZAGEN 15 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
           <t>SKU-39A56CF7E6EE</t>
         </is>
       </c>
@@ -10711,7 +10991,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10872,6 +11152,11 @@
       <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="inlineStr">
         <is>
+          <t>MIRENA 52 MG INTRAUTERINE DELIVERY SYSTEM (IUS)</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
           <t>SKU-BFFD1151046B</t>
         </is>
       </c>
@@ -10899,7 +11184,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11068,6 +11353,11 @@
       <c r="AQ58" t="inlineStr"/>
       <c r="AR58" t="inlineStr">
         <is>
+          <t>MIXTARD 30</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
           <t>SKU-53DF08E8CDA4</t>
         </is>
       </c>
@@ -11095,7 +11385,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11252,6 +11542,11 @@
       <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="inlineStr">
         <is>
+          <t>MIRAGEL 2% ORAL GEL</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
           <t>SKU-4C663D0C4FC3</t>
         </is>
       </c>
@@ -11279,7 +11574,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11436,6 +11731,11 @@
       <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="inlineStr">
         <is>
+          <t>MINOXIL 5% SOLUTION</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
           <t>SKU-23252F298622</t>
         </is>
       </c>
@@ -11463,7 +11763,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11620,6 +11920,11 @@
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr">
         <is>
+          <t>MINIRIN NASAL SPRAY 0.1MG-ML</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
           <t>SKU-9E344439F425</t>
         </is>
       </c>
@@ -11647,7 +11952,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11804,6 +12109,11 @@
       <c r="AQ62" t="inlineStr"/>
       <c r="AR62" t="inlineStr">
         <is>
+          <t>MINIRIN MILT 60 MCG LYOPHILIZED TABLET</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
           <t>SKU-D84CEE07E3D0</t>
         </is>
       </c>
@@ -11831,7 +12141,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11984,6 +12294,11 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
+          <t>NORVIR 80MG-ML ORAL SOLN.</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
           <t>SKU-4CD2DA8D175B</t>
         </is>
       </c>
@@ -12011,7 +12326,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12182,6 +12497,11 @@
       </c>
       <c r="AR64" t="inlineStr">
         <is>
+          <t>MIXTARD 30 PENFILL</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
           <t>SKU-CD787A04B0C6</t>
         </is>
       </c>
@@ -12209,7 +12529,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12358,6 +12678,11 @@
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="inlineStr">
         <is>
+          <t>MONOCEF 500MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
           <t>SKU-A45985C687C6</t>
         </is>
       </c>
@@ -12385,7 +12710,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12530,6 +12855,11 @@
       <c r="AQ66" t="inlineStr"/>
       <c r="AR66" t="inlineStr">
         <is>
+          <t>MONOCEF 250MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
           <t>SKU-7BCF0FB1BDEA</t>
         </is>
       </c>
@@ -12557,7 +12887,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12706,6 +13036,11 @@
       <c r="AQ67" t="inlineStr"/>
       <c r="AR67" t="inlineStr">
         <is>
+          <t>MONOCEF 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
           <t>SKU-9891F83E252F</t>
         </is>
       </c>
@@ -12733,7 +13068,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12886,6 +13221,11 @@
       </c>
       <c r="AR68" t="inlineStr">
         <is>
+          <t>MONOCEF 125MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
           <t>SKU-74E1EE803C82</t>
         </is>
       </c>
@@ -12913,7 +13253,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13066,6 +13406,11 @@
       <c r="AQ69" t="inlineStr"/>
       <c r="AR69" t="inlineStr">
         <is>
+          <t>MOMETAMED 0.1% W-W CREAM</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
           <t>SKU-77D5233C39DC</t>
         </is>
       </c>
@@ -13093,7 +13438,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13250,6 +13595,11 @@
       <c r="AQ70" t="inlineStr"/>
       <c r="AR70" t="inlineStr">
         <is>
+          <t>MODURETIC 5-50MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
           <t>SKU-D4AD2B9429CD</t>
         </is>
       </c>
@@ -13277,7 +13627,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13440,6 +13790,11 @@
       <c r="AQ71" t="inlineStr"/>
       <c r="AR71" t="inlineStr">
         <is>
+          <t>MOBIC 7.5MG TAB</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
           <t>SKU-366E960A560C</t>
         </is>
       </c>
@@ -13467,7 +13822,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13634,6 +13989,11 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
+          <t>MOBIC 15MG TAB</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
           <t>SKU-4ACF4E7178E3</t>
         </is>
       </c>
@@ -13661,7 +14021,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13822,6 +14182,11 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
+          <t>MOFETAB 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
           <t>SKU-21C7ED8DBFBC</t>
         </is>
       </c>
@@ -13849,7 +14214,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14006,6 +14371,11 @@
       <c r="AQ74" t="inlineStr"/>
       <c r="AR74" t="inlineStr">
         <is>
+          <t>LACTULOSE syrup</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
           <t>SKU-2024C7BCE1A4</t>
         </is>
       </c>
@@ -14033,7 +14403,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14182,6 +14552,11 @@
       <c r="AQ75" t="inlineStr"/>
       <c r="AR75" t="inlineStr">
         <is>
+          <t>UNIFED DM SYRUP</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
           <t>SKU-E42E3779611F</t>
         </is>
       </c>
@@ -14209,7 +14584,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14370,6 +14745,11 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
+          <t>UNI FRESH 0.5% UNIT DOSE EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
           <t>SKU-7BD5CA3F4242</t>
         </is>
       </c>
@@ -14397,7 +14777,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14546,6 +14926,11 @@
       <c r="AQ77" t="inlineStr"/>
       <c r="AR77" t="inlineStr">
         <is>
+          <t>UNIFED SYRUP</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
           <t>SKU-F2E5D49DD063</t>
         </is>
       </c>
@@ -14573,7 +14958,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14730,6 +15115,11 @@
       <c r="AQ78" t="inlineStr"/>
       <c r="AR78" t="inlineStr">
         <is>
+          <t>UNIPROST 4 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
           <t>SKU-66E28F8DE6CF</t>
         </is>
       </c>
@@ -14757,7 +15147,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14910,6 +15300,11 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
+          <t>UNITUM 5% GEL</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
           <t>SKU-604E7FC3D0BF</t>
         </is>
       </c>
@@ -14937,7 +15332,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15082,6 +15477,11 @@
       <c r="AQ80" t="inlineStr"/>
       <c r="AR80" t="inlineStr">
         <is>
+          <t>V-2 PLUS CAPS</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
           <t>SKU-512A1378AC2E</t>
         </is>
       </c>
@@ -15109,7 +15509,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15258,6 +15658,11 @@
       <c r="AQ81" t="inlineStr"/>
       <c r="AR81" t="inlineStr">
         <is>
+          <t>V-2 CAPS</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
           <t>SKU-C11EE8C9E59C</t>
         </is>
       </c>
@@ -15285,7 +15690,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15450,6 +15855,11 @@
       </c>
       <c r="AR82" t="inlineStr">
         <is>
+          <t>UVAMIN 100MG RETARD CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
           <t>SKU-5F85AA947E80</t>
         </is>
       </c>
@@ -15477,7 +15887,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15638,6 +16048,11 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
+          <t>URSOFALK 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
           <t>SKU-F95A4C7E29DE</t>
         </is>
       </c>
@@ -15665,7 +16080,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15826,6 +16241,11 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
+          <t>URITAB XL 10MG EXTENDED RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
           <t>SKU-2262FF9009AB</t>
         </is>
       </c>
@@ -15853,7 +16273,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16014,6 +16434,11 @@
       </c>
       <c r="AR85" t="inlineStr">
         <is>
+          <t>URILAX 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
           <t>SKU-A2D19A16BA9B</t>
         </is>
       </c>
@@ -16041,7 +16466,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16202,6 +16627,11 @@
       <c r="AQ86" t="inlineStr"/>
       <c r="AR86" t="inlineStr">
         <is>
+          <t>URALYT-U GRANULES</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
           <t>SKU-523291CCEC5C</t>
         </is>
       </c>
@@ -16229,7 +16659,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16382,6 +16812,11 @@
       </c>
       <c r="AR87" t="inlineStr">
         <is>
+          <t>UNIZYM SYRUP</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
           <t>SKU-6ABAF229865C</t>
         </is>
       </c>
@@ -16409,7 +16844,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16554,6 +16989,11 @@
       <c r="AQ88" t="inlineStr"/>
       <c r="AR88" t="inlineStr">
         <is>
+          <t>UNIVIT-E 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
           <t>SKU-B2D3E15035FC</t>
         </is>
       </c>
@@ -16581,7 +17021,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16738,6 +17178,11 @@
       <c r="AQ89" t="inlineStr"/>
       <c r="AR89" t="inlineStr">
         <is>
+          <t>UNIVIT-A FORT 50000 I.U. CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
           <t>SKU-CAD9BE90C3D1</t>
         </is>
       </c>
@@ -16765,7 +17210,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16918,6 +17363,11 @@
       </c>
       <c r="AR90" t="inlineStr">
         <is>
+          <t>UNITUM VERDE 7.5 MG/5ML MOUTHWASH AND GARGLE</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
           <t>SKU-A558B53A2D17</t>
         </is>
       </c>
@@ -16945,7 +17395,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17106,6 +17556,11 @@
       </c>
       <c r="AR91" t="inlineStr">
         <is>
+          <t>URILAX 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
           <t>SKU-F951F0B31E54</t>
         </is>
       </c>
@@ -17133,7 +17588,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17294,6 +17749,11 @@
       </c>
       <c r="AR92" t="inlineStr">
         <is>
+          <t>TYMER 0.3% EYE DROP</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
           <t>SKU-547E8B1ADFB7</t>
         </is>
       </c>
@@ -17321,7 +17781,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17478,6 +17938,11 @@
       <c r="AQ93" t="inlineStr"/>
       <c r="AR93" t="inlineStr">
         <is>
+          <t>TYLENOL SUPP 350 MG</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
           <t>SKU-0CBF437034C7</t>
         </is>
       </c>
@@ -17505,7 +17970,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17666,6 +18131,11 @@
       </c>
       <c r="AR94" t="inlineStr">
         <is>
+          <t>TYLENOL SUPP 200 MG</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
           <t>SKU-AA47075654C3</t>
         </is>
       </c>
@@ -17693,7 +18163,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17858,6 +18328,11 @@
       <c r="AQ95" t="inlineStr"/>
       <c r="AR95" t="inlineStr">
         <is>
+          <t>TYLENOL SUPP 100 MG</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
           <t>SKU-A043791EA337</t>
         </is>
       </c>
@@ -17885,7 +18360,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18034,6 +18509,11 @@
       <c r="AQ96" t="inlineStr"/>
       <c r="AR96" t="inlineStr">
         <is>
+          <t>TYLENOL FORTE TAB 500MG</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
           <t>SKU-0E0A5379411B</t>
         </is>
       </c>
@@ -18061,7 +18541,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18224,6 +18704,11 @@
       </c>
       <c r="AR97" t="inlineStr">
         <is>
+          <t>TWYNSTA</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
           <t>SKU-D0174C29C32C</t>
         </is>
       </c>
@@ -18251,7 +18736,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18414,6 +18899,11 @@
       </c>
       <c r="AR98" t="inlineStr">
         <is>
+          <t>TWYNSTA</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
           <t>SKU-A77E01A5139C</t>
         </is>
       </c>
@@ -18441,7 +18931,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18602,6 +19092,11 @@
       <c r="AQ99" t="inlineStr"/>
       <c r="AR99" t="inlineStr">
         <is>
+          <t>TWINRIX ADULT MONODOSE PREFLLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
           <t>SKU-A74275721AB4</t>
         </is>
       </c>
@@ -18629,7 +19124,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18778,6 +19273,11 @@
       <c r="AQ100" t="inlineStr"/>
       <c r="AR100" t="inlineStr">
         <is>
+          <t>TRUXAL TABLETS 50MG</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
           <t>SKU-84AD2D313276</t>
         </is>
       </c>
@@ -18805,7 +19305,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18957,6 +19457,11 @@
       </c>
       <c r="AQ101" t="inlineStr"/>
       <c r="AR101" t="inlineStr">
+        <is>
+          <t>TRIVASTAL RETARD 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
         <is>
           <t>SKU-4E3CB63F58D9</t>
         </is>
@@ -18973,7 +19478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19019,100 +19524,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19144,7 +19654,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19159,92 +19669,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-62737</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>161.76</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>596</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19276,7 +19791,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19291,92 +19806,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-92219</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>438.84</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>597</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19408,7 +19928,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19423,92 +19943,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-75386</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>349.28</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>598</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19540,7 +20065,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19555,92 +20080,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-89053</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>312.62</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>599</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19672,7 +20202,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19687,92 +20217,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-31723</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>143.42</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Wound Care</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>600</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19804,7 +20339,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19819,92 +20354,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-70401</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>233.04</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>601</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19936,7 +20476,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19951,92 +20491,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-53926</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>294.01</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>602</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20068,7 +20613,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20083,92 +20628,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-67016</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>103.18</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>603</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20200,7 +20750,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20215,92 +20765,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-72213</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>222.31</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>604</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20332,7 +20887,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20347,92 +20902,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-13733</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>150.61</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>605</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20464,7 +21024,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20479,92 +21039,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-32998</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>176.69</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>606</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20596,7 +21161,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -20611,92 +21176,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-90084</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>297.91</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>607</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20713,7 +21283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20819,6 +21389,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20854,7 +21434,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20919,6 +21499,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-53C3C6A3DD4F</t>
         </is>
@@ -20955,7 +21545,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21020,6 +21610,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-3454B7E30C22</t>
         </is>
@@ -21056,7 +21656,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21121,6 +21721,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-DCF4CF604F00</t>
         </is>
@@ -21157,7 +21767,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21222,6 +21832,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-9A3A2A99BD6D</t>
         </is>
@@ -21258,7 +21878,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21323,6 +21943,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-99DE8C908EE3</t>
         </is>
@@ -21359,7 +21989,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21424,6 +22054,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-A3BEECD7DF1F</t>
         </is>
@@ -21460,7 +22100,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21525,6 +22165,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-6FD1152B781E</t>
         </is>
@@ -21561,7 +22211,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21626,6 +22276,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-28EF434F0C73</t>
         </is>
@@ -21662,7 +22322,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21727,6 +22387,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-A67090517315</t>
         </is>
@@ -21763,7 +22433,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21828,6 +22498,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-D278D37B589B</t>
         </is>
@@ -21864,7 +22544,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21929,6 +22609,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-E3618C6C6C69</t>
         </is>
@@ -21965,7 +22655,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22030,6 +22720,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-6EEBBCB88FAD</t>
         </is>
@@ -22066,7 +22766,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22131,6 +22831,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-FA428E4AA28D</t>
         </is>
@@ -22167,7 +22877,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22232,6 +22942,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-1C00BBC8965B</t>
         </is>
@@ -22268,7 +22988,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22333,6 +23053,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-D0BB91743296</t>
         </is>
@@ -22369,7 +23099,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22434,6 +23164,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-5738794B8937</t>
         </is>
@@ -22470,7 +23210,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22535,6 +23275,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-0C9CECF33885</t>
         </is>
@@ -22571,7 +23321,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22636,6 +23386,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-AD067D1627B1</t>
         </is>
@@ -22672,7 +23432,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22737,6 +23497,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-EC9DB1266A48</t>
         </is>
@@ -22773,7 +23543,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22838,6 +23608,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-07B01EF21257</t>
         </is>

--- a/product_upload/packages/6/file.xlsx
+++ b/product_upload/packages/6/file.xlsx
@@ -680,8 +680,16 @@
           <t>7000000282-60-100000073665</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MIMPARA 60MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -861,8 +869,16 @@
           <t>7000000282-90-100000073665</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MIMPARA 90MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1235,8 +1251,16 @@
           <t>7000001155-0.9-100000073759</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MINIMS SODIUM CHLORIDE 0.9% detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1420,8 +1444,16 @@
           <t>7000001003-2-100000073759</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MINIMS PILOCARPINE 2% detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1601,8 +1633,16 @@
           <t>7000000998-10-100000073759</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MINIMS PHENYLEPHRINE HCL 10% detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1786,8 +1826,16 @@
           <t>7000000998-2.5-100000073759</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MINIMS PHENYLEPHRINE 2.5% W-V detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2357,8 +2405,16 @@
           <t>7000000536-2-100000073759</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>MINIMS FLUORESCEIN SODIUM 2% detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2731,8 +2787,16 @@
           <t>7000000335-0.5-100000073759</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MINIMS CYCLOPENTOLATE HCL 0.5% detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3294,8 +3358,16 @@
           <t>14000001294-4.25-100000073759</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>MINIMS LIDOCAINE and FLUORESCEIN detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3664,8 +3736,16 @@
           <t>14000001833-52.5-100000073664</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>MICARDIS PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -5401,8 +5481,16 @@
           <t>7000000839-10-100000073665</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>METOSIL TAB 10MG detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5771,8 +5859,16 @@
           <t>7000000366-240-100000073682</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>MINIRIN MELT 240MCG ORAL LYOPHILISATE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6137,8 +6233,16 @@
           <t>7000001067-5-100000073372</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>MUCOFALK detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6314,8 +6418,16 @@
           <t>7000001067-5-100000073372</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>MUCOFALK detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6684,8 +6796,16 @@
           <t>7000000803-7.5-100000073375</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>MOVEN 7.5MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6861,8 +6981,16 @@
           <t>7000000803-7.5-100000073375</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>MOVEN 7.5MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7046,8 +7174,16 @@
           <t>7000000803-15-100000073375</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>MOVEN 15MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7223,8 +7359,16 @@
           <t>7000000803-15-100000073375</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>MOVEN 15MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -8558,8 +8702,16 @@
           <t>7000000172-0.8-100000073652</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>MUCOFREE 4MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -10062,8 +10214,16 @@
           <t>105000024582-1519-100000073652</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>MULTIVITOL FORTE SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -12149,8 +12309,16 @@
           <t>7000001110-80-200000002007</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>NORVIR 80MG-ML ORAL SOLN. detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12537,8 +12705,16 @@
           <t>7000000228-500-200000016452</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>MONOCEF 500MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12718,8 +12894,16 @@
           <t>7000000228-50-200000017703</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>MONOCEF 250MG-5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12895,8 +13079,16 @@
           <t>7000000228-250-200000016452</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>MONOCEF 250MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13076,8 +13268,16 @@
           <t>7000000228-25-200000017703</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>MONOCEF 125MG-5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13261,8 +13461,16 @@
           <t>7000000858-0.1-100000073712</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>MOMETAMED 0.1% W-W CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -14411,8 +14619,16 @@
           <t>21000003848-8.25-100000073652</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>UNIFED DM SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14785,8 +15001,16 @@
           <t>14000003471-6.25-100000073652</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>UNIFED SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15155,8 +15379,16 @@
           <t>7000000135-5-100000073726</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>UNITUM 5% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15340,8 +15572,16 @@
           <t>161000040784-797-200000016452</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>V-2 PLUS CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15517,8 +15757,16 @@
           <t>161000040784-642-200000016452</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>V-2 CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16667,8 +16915,16 @@
           <t>35000010923-32-100000073652</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>UNIZYM SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16852,8 +17108,16 @@
           <t>7000000411-100-200000016452</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>UNIVIT-E 100MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17218,8 +17482,16 @@
           <t>7000000135-1.5-100000073677</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>UNITUM VERDE 7.5 MG/5ML MOUTHWASH AND GARGLE detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -18368,8 +18640,16 @@
           <t>7000000961-500-100000073664</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>TYLENOL FORTE TAB 500MG detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19132,8 +19412,16 @@
           <t>7000000271-50-100000073665</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>TRUXAL TABLETS 50MG detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19313,8 +19601,16 @@
           <t>7000001013-50-100000073683</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>TRIVASTAL RETARD 50MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/6/file.xlsx
+++ b/product_upload/packages/6/file.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21579,7 +21579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21660,40 +21660,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21773,38 +21778,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>163.17</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-53C3C6A3DD4F</t>
         </is>
@@ -21884,38 +21894,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>110.95</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-3454B7E30C22</t>
         </is>
@@ -21995,38 +22010,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>418.43</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-DCF4CF604F00</t>
         </is>
@@ -22106,38 +22126,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>440.37</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-9A3A2A99BD6D</t>
         </is>
@@ -22217,38 +22242,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>243.18</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-99DE8C908EE3</t>
         </is>
@@ -22328,38 +22358,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>409.4</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-A3BEECD7DF1F</t>
         </is>
@@ -22439,38 +22474,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>50.27</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-6FD1152B781E</t>
         </is>
@@ -22550,38 +22590,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>279.49</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-28EF434F0C73</t>
         </is>
@@ -22661,38 +22706,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>227.8</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-A67090517315</t>
         </is>
@@ -22772,38 +22822,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>453.2</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-D278D37B589B</t>
         </is>
@@ -22883,38 +22938,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>281.43</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-E3618C6C6C69</t>
         </is>
@@ -22994,38 +23054,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>172.83</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-6EEBBCB88FAD</t>
         </is>
@@ -23105,38 +23170,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>179.61</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-FA428E4AA28D</t>
         </is>
@@ -23216,38 +23286,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>83.84</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-1C00BBC8965B</t>
         </is>
@@ -23327,38 +23402,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>101.85</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-D0BB91743296</t>
         </is>
@@ -23438,38 +23518,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>364.68</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-5738794B8937</t>
         </is>
@@ -23549,38 +23634,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>331.36</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-0C9CECF33885</t>
         </is>
@@ -23660,38 +23750,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>304.11</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-AD067D1627B1</t>
         </is>
@@ -23771,38 +23866,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>354.81</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-EC9DB1266A48</t>
         </is>
@@ -23882,38 +23982,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>73.84</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-07B01EF21257</t>
         </is>
